--- a/legacy/Forecast-03072026-12Z.xlsx
+++ b/legacy/Forecast-03072026-12Z.xlsx
@@ -644,7 +644,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 03/07/2026 23:17</t>
+          <t>Généré le : 04/07/2026 00:11</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 03/07/2026 23:17</t>
+          <t>Généré le : 04/07/2026 00:11</t>
         </is>
       </c>
     </row>
